--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -143,16 +143,16 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -812,16 +812,16 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -866,16 +866,16 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -889,16 +889,16 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -943,16 +943,16 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -966,7 +966,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1043,10 +1043,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1097,10 +1097,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>-1</v>
@@ -1120,16 +1120,16 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>-1</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -1174,16 +1174,16 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>-1</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1197,10 +1197,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1251,10 +1251,10 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1274,10 +1274,10 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -1328,10 +1328,10 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>-1</v>
@@ -1351,10 +1351,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>-1</v>
@@ -1405,10 +1405,10 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>-1</v>
@@ -1428,10 +1428,10 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>-1</v>
@@ -1482,10 +1482,10 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>-1</v>
@@ -1505,7 +1505,7 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1582,10 +1582,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1636,10 +1636,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>-1</v>
@@ -1659,10 +1659,10 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>-1</v>
@@ -1713,10 +1713,10 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>-1</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1813,7 +1813,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -1890,7 +1890,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -1967,10 +1967,10 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>-1</v>
@@ -2021,10 +2021,10 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>-1</v>
@@ -2044,16 +2044,16 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -2098,16 +2098,16 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>-1</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2121,10 +2121,10 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>-1</v>
@@ -2175,10 +2175,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>-1</v>
@@ -2198,10 +2198,10 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>-1</v>
@@ -2252,10 +2252,10 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>-1</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2358,27 +2358,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
       <c r="I3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2387,22 +2390,25 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>6.8</v>
+      </c>
       <c r="I4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2416,27 +2422,30 @@
         <v>19</v>
       </c>
       <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>68.42</v>
+      </c>
+      <c r="G5">
+        <v>31.58</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>19</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2445,25 +2454,25 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>5.26</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>94.73999999999999</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2505,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2566,7 +2575,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -2574,219 +2583,219 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920320</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>42</v>
@@ -2794,199 +2803,199 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920320</v>
+        <v>20330051920323</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920320</v>
+        <v>20330051920323</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920321</v>
+        <v>20330051920323</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920321</v>
+        <v>20330051920324</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920321</v>
+        <v>20330051920324</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920322</v>
+        <v>20330051920324</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920322</v>
+        <v>20330051920325</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920322</v>
+        <v>20330051920325</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
@@ -2994,36 +3003,36 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920322</v>
+        <v>20330051920325</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -3034,96 +3043,96 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920380</v>
+        <v>20330051920326</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -3134,139 +3143,139 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920380</v>
+        <v>20330051920326</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920380</v>
+        <v>20330051920326</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920380</v>
+        <v>20330051920327</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920380</v>
+        <v>20330051920327</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920324</v>
+        <v>20330051920327</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
         <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920324</v>
+        <v>20330051920328</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920324</v>
+        <v>20330051920328</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
         <v>42</v>
@@ -3274,19 +3283,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920324</v>
+        <v>20330051920328</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
         <v>44</v>
@@ -3294,79 +3303,79 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920324</v>
+        <v>20330051920328</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920325</v>
+        <v>20330051920328</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920325</v>
+        <v>20330051920396</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920325</v>
+        <v>20330051920396</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
         <v>42</v>
@@ -3374,19 +3383,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920325</v>
+        <v>20330051920396</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
         <v>44</v>
@@ -3394,36 +3403,36 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920325</v>
+        <v>20330051920396</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920397</v>
+        <v>20330051920329</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -3434,259 +3443,259 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920397</v>
+        <v>20330051920329</v>
       </c>
       <c r="B47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920397</v>
+        <v>20330051920329</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920397</v>
+        <v>20330051920329</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920397</v>
+        <v>20330051920330</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920397</v>
+        <v>20330051920330</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E51" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920326</v>
+        <v>20330051920330</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920326</v>
+        <v>20330051920331</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920326</v>
+        <v>20330051920331</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D54" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920326</v>
+        <v>20330051920333</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920326</v>
+        <v>20330051920333</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920327</v>
+        <v>20330051920333</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920327</v>
+        <v>20330051920335</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920327</v>
+        <v>20330051920335</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
         <v>42</v>
@@ -3694,762 +3703,22 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920327</v>
+        <v>20330051920335</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D60" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920327</v>
-      </c>
-      <c r="B61" t="s">
-        <v>60</v>
-      </c>
-      <c r="C61" t="s">
-        <v>57</v>
-      </c>
-      <c r="D61" t="s">
-        <v>94</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920328</v>
-      </c>
-      <c r="B62" t="s">
-        <v>61</v>
-      </c>
-      <c r="C62" t="s">
-        <v>77</v>
-      </c>
-      <c r="D62" t="s">
-        <v>95</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920328</v>
-      </c>
-      <c r="B63" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" t="s">
-        <v>77</v>
-      </c>
-      <c r="D63" t="s">
-        <v>95</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920328</v>
-      </c>
-      <c r="B64" t="s">
-        <v>61</v>
-      </c>
-      <c r="C64" t="s">
-        <v>77</v>
-      </c>
-      <c r="D64" t="s">
-        <v>95</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920328</v>
-      </c>
-      <c r="B65" t="s">
-        <v>61</v>
-      </c>
-      <c r="C65" t="s">
-        <v>77</v>
-      </c>
-      <c r="D65" t="s">
-        <v>95</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920328</v>
-      </c>
-      <c r="B66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" t="s">
-        <v>77</v>
-      </c>
-      <c r="D66" t="s">
-        <v>95</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920328</v>
-      </c>
-      <c r="B67" t="s">
-        <v>61</v>
-      </c>
-      <c r="C67" t="s">
-        <v>77</v>
-      </c>
-      <c r="D67" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920396</v>
-      </c>
-      <c r="B68" t="s">
-        <v>62</v>
-      </c>
-      <c r="C68" t="s">
-        <v>76</v>
-      </c>
-      <c r="D68" t="s">
-        <v>96</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920396</v>
-      </c>
-      <c r="B69" t="s">
-        <v>62</v>
-      </c>
-      <c r="C69" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" t="s">
-        <v>96</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920396</v>
-      </c>
-      <c r="B70" t="s">
-        <v>62</v>
-      </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" t="s">
-        <v>96</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920396</v>
-      </c>
-      <c r="B71" t="s">
-        <v>62</v>
-      </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920396</v>
-      </c>
-      <c r="B72" t="s">
-        <v>62</v>
-      </c>
-      <c r="C72" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" t="s">
-        <v>96</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920329</v>
-      </c>
-      <c r="B73" t="s">
-        <v>63</v>
-      </c>
-      <c r="C73" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" t="s">
-        <v>97</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920329</v>
-      </c>
-      <c r="B74" t="s">
-        <v>63</v>
-      </c>
-      <c r="C74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920329</v>
-      </c>
-      <c r="B75" t="s">
-        <v>63</v>
-      </c>
-      <c r="C75" t="s">
-        <v>78</v>
-      </c>
-      <c r="D75" t="s">
-        <v>97</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920329</v>
-      </c>
-      <c r="B76" t="s">
-        <v>63</v>
-      </c>
-      <c r="C76" t="s">
-        <v>78</v>
-      </c>
-      <c r="D76" t="s">
-        <v>97</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920329</v>
-      </c>
-      <c r="B77" t="s">
-        <v>63</v>
-      </c>
-      <c r="C77" t="s">
-        <v>78</v>
-      </c>
-      <c r="D77" t="s">
-        <v>97</v>
-      </c>
-      <c r="E77" t="s">
-        <v>6</v>
-      </c>
-      <c r="F77" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920330</v>
-      </c>
-      <c r="B78" t="s">
-        <v>64</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" t="s">
-        <v>98</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920330</v>
-      </c>
-      <c r="B79" t="s">
-        <v>64</v>
-      </c>
-      <c r="C79" t="s">
-        <v>79</v>
-      </c>
-      <c r="D79" t="s">
-        <v>98</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920330</v>
-      </c>
-      <c r="B80" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" t="s">
-        <v>79</v>
-      </c>
-      <c r="D80" t="s">
-        <v>98</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920330</v>
-      </c>
-      <c r="B81" t="s">
-        <v>64</v>
-      </c>
-      <c r="C81" t="s">
-        <v>79</v>
-      </c>
-      <c r="D81" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920330</v>
-      </c>
-      <c r="B82" t="s">
-        <v>64</v>
-      </c>
-      <c r="C82" t="s">
-        <v>79</v>
-      </c>
-      <c r="D82" t="s">
-        <v>98</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920331</v>
-      </c>
-      <c r="B83" t="s">
-        <v>65</v>
-      </c>
-      <c r="C83" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" t="s">
-        <v>99</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920331</v>
-      </c>
-      <c r="B84" t="s">
-        <v>65</v>
-      </c>
-      <c r="C84" t="s">
-        <v>80</v>
-      </c>
-      <c r="D84" t="s">
-        <v>99</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920331</v>
-      </c>
-      <c r="B85" t="s">
-        <v>65</v>
-      </c>
-      <c r="C85" t="s">
-        <v>80</v>
-      </c>
-      <c r="D85" t="s">
-        <v>99</v>
-      </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920331</v>
-      </c>
-      <c r="B86" t="s">
-        <v>65</v>
-      </c>
-      <c r="C86" t="s">
-        <v>80</v>
-      </c>
-      <c r="D86" t="s">
-        <v>99</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920331</v>
-      </c>
-      <c r="B87" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" t="s">
-        <v>80</v>
-      </c>
-      <c r="D87" t="s">
-        <v>99</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920333</v>
-      </c>
-      <c r="B88" t="s">
-        <v>66</v>
-      </c>
-      <c r="C88" t="s">
-        <v>81</v>
-      </c>
-      <c r="D88" t="s">
-        <v>100</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920333</v>
-      </c>
-      <c r="B89" t="s">
-        <v>66</v>
-      </c>
-      <c r="C89" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" t="s">
-        <v>100</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920333</v>
-      </c>
-      <c r="B90" t="s">
-        <v>66</v>
-      </c>
-      <c r="C90" t="s">
-        <v>81</v>
-      </c>
-      <c r="D90" t="s">
-        <v>100</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920333</v>
-      </c>
-      <c r="B91" t="s">
-        <v>66</v>
-      </c>
-      <c r="C91" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" t="s">
-        <v>100</v>
-      </c>
-      <c r="E91" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920333</v>
-      </c>
-      <c r="B92" t="s">
-        <v>66</v>
-      </c>
-      <c r="C92" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" t="s">
-        <v>100</v>
-      </c>
-      <c r="E92" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920335</v>
-      </c>
-      <c r="B93" t="s">
-        <v>67</v>
-      </c>
-      <c r="C93" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93" t="s">
-        <v>101</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920335</v>
-      </c>
-      <c r="B94" t="s">
-        <v>67</v>
-      </c>
-      <c r="C94" t="s">
-        <v>82</v>
-      </c>
-      <c r="D94" t="s">
-        <v>101</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920335</v>
-      </c>
-      <c r="B95" t="s">
-        <v>67</v>
-      </c>
-      <c r="C95" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" t="s">
-        <v>101</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920335</v>
-      </c>
-      <c r="B96" t="s">
-        <v>67</v>
-      </c>
-      <c r="C96" t="s">
-        <v>82</v>
-      </c>
-      <c r="D96" t="s">
-        <v>101</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920335</v>
-      </c>
-      <c r="B97" t="s">
-        <v>67</v>
-      </c>
-      <c r="C97" t="s">
-        <v>82</v>
-      </c>
-      <c r="D97" t="s">
-        <v>101</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4497,7 +3766,7 @@
         <v>92</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4514,58 +3783,58 @@
         <v>95</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920317</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920318</v>
+        <v>20330051920396</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920320</v>
+        <v>20330051920329</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4582,7 +3851,7 @@
         <v>86</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4599,211 +3868,211 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920380</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920396</v>
+        <v>20330051920333</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920329</v>
+        <v>20330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920330</v>
+        <v>20330051920317</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920331</v>
+        <v>20330051920318</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920333</v>
+        <v>20330051920322</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920335</v>
+        <v>20330051920380</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920322</v>
+        <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4813,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4843,6 +4112,190 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920317</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920317</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920322</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920322</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920380</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920380</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920331</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920331</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -140,16 +140,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>
@@ -818,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -895,7 +895,7 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -949,7 +949,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1049,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -1103,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1180,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>-1</v>
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -1488,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -1588,7 +1588,7 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -1642,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -1719,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>-1</v>
@@ -1896,7 +1896,7 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -1950,7 +1950,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -1973,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2027,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -2104,7 +2104,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2127,7 +2127,7 @@
         <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -2181,7 +2181,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2258,7 +2258,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2329,27 +2329,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
       <c r="I2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2358,30 +2361,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>5.26</v>
+        <v>21.05</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>94.73999999999999</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2390,30 +2393,30 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>68.42</v>
+      </c>
+      <c r="G4">
+        <v>31.58</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>21.05</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>6.8</v>
-      </c>
-      <c r="I4">
-        <v>15</v>
-      </c>
-      <c r="J4">
-        <v>78.95</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -2422,25 +2425,25 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G5">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2514,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2555,7 +2558,7 @@
         <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>40</v>
@@ -2563,59 +2566,59 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>41</v>
@@ -2635,10 +2638,10 @@
         <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2655,107 +2658,107 @@
         <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920321</v>
+        <v>20330051920323</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>41</v>
@@ -2763,19 +2766,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B13" t="s">
         <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
@@ -2783,79 +2786,79 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920322</v>
+        <v>20330051920380</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920323</v>
+        <v>20330051920325</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>41</v>
@@ -2863,19 +2866,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920380</v>
+        <v>20330051920325</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
@@ -2883,219 +2886,219 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920380</v>
+        <v>20330051920397</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920397</v>
+        <v>20330051920327</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920397</v>
+        <v>20330051920327</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>41</v>
@@ -3103,39 +3106,39 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920326</v>
+        <v>20330051920328</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
         <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
         <v>40</v>
@@ -3143,179 +3146,179 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920326</v>
+        <v>20330051920328</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
         <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920327</v>
+        <v>20330051920396</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920327</v>
+        <v>20330051920396</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920327</v>
+        <v>20330051920396</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920328</v>
+        <v>20330051920329</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920328</v>
+        <v>20330051920329</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920328</v>
+        <v>20330051920329</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920328</v>
+        <v>20330051920330</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
         <v>41</v>
@@ -3323,39 +3326,39 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920328</v>
+        <v>20330051920330</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920396</v>
+        <v>20330051920331</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>40</v>
@@ -3363,59 +3366,59 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920396</v>
+        <v>20330051920333</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920396</v>
+        <v>20330051920333</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920396</v>
+        <v>20330051920335</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
         <v>41</v>
@@ -3423,302 +3426,22 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920329</v>
+        <v>20330051920335</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920329</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" t="s">
-        <v>78</v>
-      </c>
-      <c r="D47" t="s">
-        <v>97</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920329</v>
-      </c>
-      <c r="B48" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" t="s">
-        <v>78</v>
-      </c>
-      <c r="D48" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920329</v>
-      </c>
-      <c r="B49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920330</v>
-      </c>
-      <c r="B50" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" t="s">
-        <v>98</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920330</v>
-      </c>
-      <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920330</v>
-      </c>
-      <c r="B52" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" t="s">
-        <v>98</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920331</v>
-      </c>
-      <c r="B53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" t="s">
-        <v>99</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920331</v>
-      </c>
-      <c r="B54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" t="s">
-        <v>99</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920333</v>
-      </c>
-      <c r="B55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920333</v>
-      </c>
-      <c r="B56" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920333</v>
-      </c>
-      <c r="B57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920335</v>
-      </c>
-      <c r="B58" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" t="s">
-        <v>82</v>
-      </c>
-      <c r="D58" t="s">
-        <v>101</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920335</v>
-      </c>
-      <c r="B59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" t="s">
-        <v>101</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920335</v>
-      </c>
-      <c r="B60" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" t="s">
-        <v>101</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3834,7 +3557,7 @@
         <v>97</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3851,157 +3574,157 @@
         <v>86</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920322</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920324</v>
+        <v>20330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920324</v>
       </c>
       <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920326</v>
+        <v>20330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920327</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920330</v>
+        <v>20330051920327</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920333</v>
+        <v>20330051920330</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920335</v>
+        <v>20330051920333</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -4009,36 +3732,36 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920318</v>
+        <v>20330051920317</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920322</v>
+        <v>20330051920318</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4055,7 +3778,7 @@
         <v>89</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4072,7 +3795,7 @@
         <v>99</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4082,7 +3805,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4114,45 +3837,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4160,22 +3883,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4183,22 +3906,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -4206,22 +3929,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920380</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4229,19 +3952,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920380</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
@@ -4252,22 +3975,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920331</v>
+        <v>20330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4275,24 +3998,415 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>20330051920323</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920324</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920325</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920325</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920326</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920326</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920327</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920327</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920330</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920330</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920333</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920333</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920335</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920335</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920317</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920380</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>20330051920331</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B26" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C26" t="s">
         <v>80</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D26" t="s">
         <v>99</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9">
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -1055,7 +1055,7 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1109,7 +1109,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1825,7 +1825,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1879,7 +1879,7 @@
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2329,25 +2329,25 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J2">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2686,22 +2686,22 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2718,24 +2718,24 @@
         <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -2758,24 +2758,24 @@
         <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920323</v>
+        <v>20330051920380</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -2786,22 +2786,22 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920380</v>
+        <v>20330051920324</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2818,30 +2818,30 @@
         <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2858,30 +2858,30 @@
         <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2898,10 +2898,10 @@
         <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2918,10 +2918,10 @@
         <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2938,10 +2938,10 @@
         <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2958,30 +2958,30 @@
         <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2998,30 +2998,30 @@
         <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3038,30 +3038,30 @@
         <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920327</v>
+        <v>20330051920328</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3078,10 +3078,10 @@
         <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3098,10 +3098,10 @@
         <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3118,10 +3118,10 @@
         <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3138,30 +3138,30 @@
         <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920328</v>
+        <v>20330051920396</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3178,10 +3178,10 @@
         <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3198,50 +3198,50 @@
         <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920396</v>
+        <v>20330051920329</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920396</v>
+        <v>20330051920329</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3258,44 +3258,44 @@
         <v>97</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920329</v>
+        <v>20330051920330</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920329</v>
+        <v>20330051920330</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -3306,56 +3306,56 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920330</v>
+        <v>20330051920331</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920331</v>
+        <v>20330051920333</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -3366,16 +3366,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -3386,61 +3386,21 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920335</v>
-      </c>
-      <c r="B45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920335</v>
-      </c>
-      <c r="B46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" t="s">
-        <v>101</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3540,7 +3500,7 @@
         <v>96</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3562,16 +3522,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3579,16 +3539,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3596,16 +3556,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -3613,16 +3573,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3630,16 +3590,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -3647,16 +3607,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3664,16 +3624,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -3681,16 +3641,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -3698,16 +3658,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -3715,33 +3675,33 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920335</v>
+        <v>20330051920317</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -3749,16 +3709,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3805,7 +3765,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3883,22 +3843,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -3906,22 +3866,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -3929,22 +3889,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -3952,22 +3912,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -3975,16 +3935,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3998,16 +3958,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4021,16 +3981,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4044,16 +4004,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4067,16 +4027,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -4090,16 +4050,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4113,16 +4073,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -4136,16 +4096,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4159,16 +4119,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -4182,16 +4142,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4205,16 +4165,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -4228,16 +4188,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -4251,16 +4211,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -4274,16 +4234,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -4297,22 +4257,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920335</v>
+        <v>20330051920317</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -4320,22 +4280,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920335</v>
+        <v>20330051920321</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -4343,16 +4303,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920317</v>
+        <v>20330051920380</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -4366,16 +4326,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920380</v>
+        <v>20330051920331</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -4384,29 +4344,6 @@
         <v>40</v>
       </c>
       <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920331</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -140,21 +140,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -170,160 +170,160 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>SILVERIO</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>GUILLERMO SAID</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
     <t>ROGELIO</t>
   </si>
   <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
     <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
@@ -824,7 +824,7 @@
         <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -878,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -901,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -955,7 +955,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -978,7 +978,7 @@
         <v>-1</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1032,7 +1032,7 @@
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1132,7 +1132,7 @@
         <v>7</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1286,7 +1286,7 @@
         <v>-1</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1340,7 +1340,7 @@
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1363,7 +1363,7 @@
         <v>-1</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1417,7 +1417,7 @@
         <v>-1</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1440,7 +1440,7 @@
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1494,7 +1494,7 @@
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1517,7 +1517,7 @@
         <v>-1</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1571,7 +1571,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1594,7 +1594,7 @@
         <v>-1</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1648,7 +1648,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1671,7 +1671,7 @@
         <v>-1</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1725,7 +1725,7 @@
         <v>-1</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1748,7 +1748,7 @@
         <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1902,7 +1902,7 @@
         <v>-1</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -1956,7 +1956,7 @@
         <v>-1</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1979,7 +1979,7 @@
         <v>-1</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2033,7 +2033,7 @@
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2056,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2110,7 +2110,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2133,7 +2133,7 @@
         <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2187,7 +2187,7 @@
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2210,7 +2210,7 @@
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>40</v>
@@ -2329,30 +2329,30 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>15.79</v>
+        <v>21.05</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2361,30 +2361,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>68.42</v>
+      </c>
+      <c r="G3">
+        <v>31.58</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>21.05</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>6.8</v>
-      </c>
-      <c r="I3">
-        <v>15</v>
-      </c>
-      <c r="J3">
-        <v>78.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2393,30 +2393,30 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G4">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2457,25 +2457,25 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>89.47</v>
+      </c>
+      <c r="G6">
+        <v>10.53</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.4</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>26.32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2546,39 +2546,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920317</v>
+        <v>20330051920320</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>40</v>
@@ -2589,16 +2589,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -2606,59 +2606,59 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920320</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
@@ -2666,99 +2666,99 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920321</v>
+        <v>20330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920322</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920322</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
         <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>40</v>
@@ -2766,59 +2766,59 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920380</v>
+        <v>20330051920397</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920324</v>
+        <v>20330051920326</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>40</v>
@@ -2826,179 +2826,179 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920325</v>
+        <v>20330051920327</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920325</v>
+        <v>20330051920328</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B18" t="s">
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B19" t="s">
         <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>40</v>
@@ -3006,39 +3006,39 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920327</v>
+        <v>20330051920329</v>
       </c>
       <c r="B25" t="s">
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
         <v>40</v>
@@ -3046,361 +3046,41 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920328</v>
+        <v>20330051920333</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920328</v>
+        <v>20330051920335</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920328</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920328</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920328</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920396</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920396</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920396</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920329</v>
-      </c>
-      <c r="B35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920329</v>
-      </c>
-      <c r="B36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>97</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920329</v>
-      </c>
-      <c r="B37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920330</v>
-      </c>
-      <c r="B38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920330</v>
-      </c>
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
-      <c r="D39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920331</v>
-      </c>
-      <c r="B40" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" t="s">
-        <v>99</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920333</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920333</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920335</v>
-      </c>
-      <c r="B43" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" t="s">
-        <v>101</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920335</v>
-      </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" t="s">
-        <v>101</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3440,16 +3120,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3457,16 +3137,16 @@
         <v>20330051920328</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3474,16 +3154,16 @@
         <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3491,13 +3171,13 @@
         <v>20330051920396</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3505,33 +3185,33 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920329</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3539,152 +3219,152 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920324</v>
+        <v>20330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920324</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920326</v>
+        <v>20330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920327</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920330</v>
+        <v>20330051920327</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920333</v>
+        <v>20330051920330</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920335</v>
+        <v>20330051920333</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -3692,36 +3372,36 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920318</v>
+        <v>20330051920317</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920321</v>
+        <v>20330051920318</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3729,16 +3409,16 @@
         <v>20330051920380</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3746,16 +3426,16 @@
         <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3765,7 +3445,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3797,42 +3477,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920318</v>
+        <v>20330051920322</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>42</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920318</v>
+        <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>40</v>
@@ -3843,68 +3523,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920322</v>
+        <v>20330051920317</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920318</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>41</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920323</v>
+        <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -3915,16 +3595,16 @@
         <v>20330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>40</v>
@@ -3938,19 +3618,19 @@
         <v>20330051920324</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -3958,19 +3638,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>40</v>
@@ -3981,22 +3661,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -4004,19 +3684,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920325</v>
+        <v>20330051920327</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>40</v>
@@ -4027,22 +3707,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920330</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -4050,19 +3730,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920326</v>
+        <v>20330051920333</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>40</v>
@@ -4073,277 +3753,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920327</v>
+        <v>20330051920335</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920327</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920330</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920333</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920333</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920335</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920335</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920317</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920321</v>
-      </c>
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920380</v>
-      </c>
-      <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920331</v>
-      </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -173,10 +173,64 @@
     <t>CANTELLAN</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>GAMEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
@@ -185,145 +239,91 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
     <t>MAYA</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>OCAÑA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>LARA</t>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>SOLIS</t>
   </si>
   <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
   </si>
   <si>
     <t>SURISADAY</t>
   </si>
   <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
     <t>JESUS SAMUEL</t>
   </si>
   <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
     <t>ARIZBETH</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
     <t>FRANCISCO YAEL</t>
   </si>
   <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
     <t>OZIEL</t>
   </si>
   <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -839,7 +839,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -875,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -916,7 +916,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -940,7 +940,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -952,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -975,13 +975,13 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1017,7 +1017,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1029,7 +1029,7 @@
         <v>-1</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1052,13 +1052,13 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1070,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1106,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1135,7 +1135,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1147,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1183,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1212,7 +1212,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1248,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1283,13 +1283,13 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1301,7 +1301,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1337,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1360,13 +1360,13 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1378,7 +1378,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1414,7 +1414,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1437,13 +1437,13 @@
         <v>7</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G12">
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1455,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1491,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1502,7 +1502,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1520,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1556,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1591,13 +1591,13 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1609,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1633,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1645,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1668,13 +1668,13 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1686,7 +1686,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1722,7 +1722,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>-1</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -1763,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1799,7 +1799,7 @@
         <v>-1</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -1822,13 +1822,13 @@
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1840,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1876,7 +1876,7 @@
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1899,13 +1899,13 @@
         <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -1917,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1941,7 +1941,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -1953,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1976,13 +1976,13 @@
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -1994,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2071,7 +2071,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2107,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2130,13 +2130,13 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2184,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2207,13 +2207,13 @@
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2225,7 +2225,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2249,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2261,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2329,25 +2329,25 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>21.05</v>
+        <v>57.89</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>31.58</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>78.95</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2489,25 +2489,25 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
     </row>
   </sheetData>
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2552,10 +2552,10 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2572,50 +2572,50 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -2626,16 +2626,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2646,16 +2646,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -2666,116 +2666,116 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920397</v>
       </c>
       <c r="B8" t="s">
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920324</v>
+        <v>20330051920328</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920328</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -2786,302 +2786,22 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920397</v>
+        <v>20330051920329</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920326</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920327</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920328</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920328</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920328</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920328</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920396</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920396</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920396</v>
-      </c>
-      <c r="B23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920329</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920329</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920330</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920333</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920335</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3120,16 +2840,16 @@
         <v>20330051920397</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3137,16 +2857,16 @@
         <v>20330051920328</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3157,44 +2877,44 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920396</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920322</v>
+        <v>20330051920396</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3205,180 +2925,180 @@
         <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
         <v>60</v>
       </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920323</v>
+        <v>20330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920324</v>
+        <v>20330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920325</v>
+        <v>20330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920380</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920327</v>
+        <v>20330051920324</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920330</v>
+        <v>20330051920325</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920333</v>
+        <v>20330051920326</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920335</v>
+        <v>20330051920327</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920317</v>
+        <v>20330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
@@ -3389,13 +3109,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920318</v>
+        <v>20330051920331</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
         <v>99</v>
@@ -3406,13 +3126,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920380</v>
+        <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>100</v>
@@ -3423,13 +3143,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920331</v>
+        <v>20330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>101</v>
@@ -3445,7 +3165,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3480,13 +3200,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3503,13 +3223,13 @@
         <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3526,13 +3246,13 @@
         <v>20330051920317</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3549,13 +3269,13 @@
         <v>20330051920318</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3572,13 +3292,13 @@
         <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -3587,21 +3307,21 @@
         <v>40</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920323</v>
+        <v>20330051920331</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3610,21 +3330,21 @@
         <v>40</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920324</v>
+        <v>20330051920335</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3633,145 +3353,7 @@
         <v>40</v>
       </c>
       <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920325</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920326</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920327</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920330</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920333</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920335</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -149,12 +149,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -182,136 +182,136 @@
     <t>MOLINA</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>IRVING</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>OZIEL</t>
@@ -830,13 +830,13 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -907,13 +907,13 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -946,10 +946,10 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -969,7 +969,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -984,10 +984,10 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1023,7 +1023,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>-1</v>
@@ -1061,13 +1061,13 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1097,13 +1097,13 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1138,13 +1138,13 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1215,10 +1215,10 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1251,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1292,13 +1292,13 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1369,13 +1369,13 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1405,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1446,13 +1446,13 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1482,13 +1482,13 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1508,10 +1508,10 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -1523,10 +1523,10 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1562,10 +1562,10 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1600,13 +1600,13 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1636,13 +1636,13 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1677,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1713,10 +1713,10 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>-1</v>
@@ -1754,10 +1754,10 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1793,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>-1</v>
@@ -1816,10 +1816,10 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1831,13 +1831,13 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1893,7 +1893,7 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -1908,10 +1908,10 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1947,7 +1947,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1985,13 +1985,13 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2021,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2062,13 +2062,13 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2098,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2139,13 +2139,13 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2175,10 +2175,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2216,10 +2216,10 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2252,10 +2252,10 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2361,19 +2361,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>68.42</v>
+        <v>57.89</v>
       </c>
       <c r="G3">
-        <v>31.58</v>
+        <v>42.11</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2393,30 +2393,30 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -2425,30 +2425,30 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>89.47</v>
+      </c>
+      <c r="G5">
+        <v>10.53</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>26.32</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2457,19 +2457,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G6">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2552,10 +2552,10 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2566,22 +2566,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2592,30 +2592,30 @@
         <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -2626,16 +2626,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -2646,162 +2646,22 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920397</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920328</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920328</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920328</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920396</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920396</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920329</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2837,19 +2697,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920397</v>
+        <v>20330051920322</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2860,13 +2720,13 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2877,75 +2737,75 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920396</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920329</v>
+        <v>20330051920318</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920317</v>
+        <v>20330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>89</v>
@@ -2956,13 +2816,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920318</v>
+        <v>20330051920323</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
@@ -2973,13 +2833,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
@@ -2990,13 +2850,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>92</v>
@@ -3007,13 +2867,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920380</v>
+        <v>20330051920325</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -3024,13 +2884,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920324</v>
+        <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>94</v>
@@ -3041,13 +2901,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920325</v>
+        <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
@@ -3058,13 +2918,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -3075,13 +2935,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920327</v>
+        <v>20330051920329</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>97</v>
@@ -3095,10 +2955,10 @@
         <v>20330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
@@ -3112,10 +2972,10 @@
         <v>20330051920331</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>99</v>
@@ -3129,10 +2989,10 @@
         <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>100</v>
@@ -3146,10 +3006,10 @@
         <v>20330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>101</v>
@@ -3165,7 +3025,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3197,39 +3057,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920322</v>
+        <v>20330051920329</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920322</v>
+        <v>20330051920329</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3238,27 +3098,27 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3266,22 +3126,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920318</v>
+        <v>20330051920335</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3289,22 +3149,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3312,22 +3172,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920331</v>
+        <v>20330051920318</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3335,16 +3195,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920335</v>
+        <v>20330051920321</v>
       </c>
       <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
         <v>78</v>
       </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3353,6 +3213,52 @@
         <v>40</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920396</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920331</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -149,10 +149,10 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -842,7 +842,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1150,7 +1150,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1227,7 +1227,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1381,7 +1381,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1458,7 +1458,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1535,7 +1535,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1571,7 +1571,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1612,7 +1612,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1689,7 +1689,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1843,7 +1843,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1879,7 +1879,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1920,7 +1920,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1997,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2033,7 +2033,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2151,7 +2151,7 @@
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2228,7 +2228,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
@@ -2425,19 +2425,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G5">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2469,7 +2469,7 @@
         <v>5.26</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3025,7 +3025,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3057,16 +3057,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -3080,16 +3080,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3098,21 +3098,21 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920335</v>
+        <v>20330051920329</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -3126,16 +3126,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920335</v>
+        <v>20330051920329</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3149,22 +3149,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3172,22 +3172,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920318</v>
+        <v>20330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3195,22 +3195,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3218,16 +3218,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920396</v>
+        <v>20330051920318</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -3241,16 +3241,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920331</v>
+        <v>20330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3259,6 +3259,52 @@
         <v>40</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920396</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920331</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -143,19 +143,19 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>NC</t>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -851,7 +851,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -860,13 +860,13 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -919,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -928,7 +928,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -943,10 +943,10 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -996,7 +996,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1005,7 +1005,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1014,13 +1014,13 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1032,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1061,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1091,16 +1091,16 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1109,7 +1109,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1138,7 +1138,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -1159,7 +1159,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1168,13 +1168,13 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1215,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1236,7 +1236,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1245,16 +1245,16 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>-1</v>
@@ -1263,7 +1263,7 @@
         <v>-1</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1292,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -1313,7 +1313,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1322,13 +1322,13 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1390,7 +1390,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1399,13 +1399,13 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1417,7 +1417,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1446,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1467,7 +1467,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1476,13 +1476,13 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1494,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1544,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1553,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1562,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1571,7 +1571,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1600,7 +1600,7 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1621,7 +1621,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1630,16 +1630,16 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -1698,7 +1698,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1707,16 +1707,16 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1725,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1754,7 +1754,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1775,7 +1775,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1784,13 +1784,13 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1802,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1831,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -1852,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1861,13 +1861,13 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>10</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1908,7 +1908,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -1929,7 +1929,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1938,13 +1938,13 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>7</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1985,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>8</v>
@@ -2006,7 +2006,7 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2015,16 +2015,16 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2083,7 +2083,7 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2092,13 +2092,13 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2110,7 +2110,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2139,7 +2139,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2169,13 +2169,13 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2187,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2237,7 +2237,7 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2246,13 +2246,13 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>8</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2264,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>41</v>
@@ -2361,30 +2361,30 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>57.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G3">
-        <v>42.11</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
@@ -2393,25 +2393,25 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>89.47</v>
+      </c>
+      <c r="G4">
+        <v>10.53</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>15.79</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2437,7 +2437,7 @@
         <v>5.26</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
@@ -2460,27 +2460,27 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>94.73999999999999</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9.1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>5.26</v>
-      </c>
-      <c r="H6">
-        <v>8.5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
@@ -2492,22 +2492,22 @@
         <v>18</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>94.73999999999999</v>
       </c>
       <c r="G7">
+        <v>5.26</v>
+      </c>
+      <c r="H7">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>9.1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2561,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2581,7 +2581,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2661,7 +2661,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3057,39 +3057,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920397</v>
+        <v>20330051920320</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920397</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3098,44 +3098,44 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920329</v>
+        <v>20330051920322</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920329</v>
+        <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3144,27 +3144,27 @@
         <v>40</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920335</v>
+        <v>20330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920335</v>
+        <v>20330051920397</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3190,7 +3190,7 @@
         <v>40</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3210,7 +3210,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3218,22 +3218,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3241,16 +3241,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920321</v>
+        <v>20330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3264,22 +3264,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920396</v>
+        <v>20330051920331</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3287,16 +3287,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920331</v>
+        <v>20330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -845,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -922,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -940,7 +940,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1017,7 +1017,7 @@
         <v>7</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1076,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1230,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1307,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1384,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1461,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1538,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1556,7 +1556,7 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1692,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1733,7 +1733,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1751,7 +1751,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1787,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1846,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1923,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2000,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2231,7 +2231,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2460,22 +2460,22 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>94.73999999999999</v>
       </c>
       <c r="G6">
+        <v>5.26</v>
+      </c>
+      <c r="H6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>9.1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
       <c r="J6">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2642,26 +2642,6 @@
       </c>
       <c r="F6" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920328</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2714,33 +2694,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920328</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920397</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2748,16 +2728,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5">
         <v>1</v>

--- a/grupos/4ASV - Estadisticos 20212.xlsx
+++ b/grupos/4ASV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -170,142 +170,142 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
     <t>MARCOS</t>
   </si>
   <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
     <t>IRVING</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
@@ -848,16 +848,16 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -866,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -925,19 +925,19 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -952,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -972,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -990,7 +990,7 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1002,16 +1002,16 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>7</v>
@@ -1020,13 +1020,13 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1079,16 +1079,16 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>5</v>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1156,16 +1156,16 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1180,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1203,10 +1203,10 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1221,10 +1221,10 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1233,16 +1233,16 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1257,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1310,16 +1310,16 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1387,16 +1387,16 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1411,10 +1411,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1464,16 +1464,16 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>7</v>
@@ -1482,7 +1482,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1491,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1514,7 +1514,7 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1529,10 +1529,10 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1541,16 +1541,16 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -1559,16 +1559,16 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1618,16 +1618,16 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1695,16 +1695,16 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1719,10 +1719,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1760,7 +1760,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -1772,16 +1772,16 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -1790,13 +1790,13 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>5</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1849,16 +1849,16 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1914,7 +1914,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -1926,16 +1926,16 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -1944,16 +1944,16 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2003,16 +2003,16 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2080,16 +2080,16 @@
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2104,10 +2104,10 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2157,16 +2157,16 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2175,13 +2175,13 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2234,16 +2234,16 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>7</v>
@@ -2258,10 +2258,10 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2329,25 +2329,25 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>57.89</v>
+        <v>78.95</v>
       </c>
       <c r="G2">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2361,25 +2361,25 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>84.20999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>10.53</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2489,19 +2489,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2517,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2542,106 +2542,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920320</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920322</v>
-      </c>
-      <c r="B4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920397</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920328</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2677,81 +2577,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920322</v>
+        <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920320</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920397</v>
+        <v>20330051920320</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920328</v>
+        <v>20330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920322</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>87</v>
@@ -2762,13 +2662,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920318</v>
+        <v>20330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>88</v>
@@ -2779,13 +2679,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
         <v>89</v>
@@ -2796,13 +2696,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
@@ -2813,13 +2713,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920380</v>
+        <v>20330051920325</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
@@ -2830,13 +2730,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
         <v>92</v>
@@ -2847,13 +2747,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -2864,10 +2764,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>57</v>
@@ -2881,13 +2781,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920327</v>
+        <v>20330051920328</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
@@ -2901,10 +2801,10 @@
         <v>20330051920396</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>96</v>
@@ -2918,10 +2818,10 @@
         <v>20330051920329</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
         <v>97</v>
@@ -2935,10 +2835,10 @@
         <v>20330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>98</v>
@@ -2952,10 +2852,10 @@
         <v>20330051920331</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>99</v>
@@ -2969,10 +2869,10 @@
         <v>20330051920333</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
         <v>100</v>
@@ -2986,10 +2886,10 @@
         <v>20330051920335</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
         <v>101</v>
@@ -3005,7 +2905,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3037,25 +2937,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920320</v>
+        <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3063,13 +2963,13 @@
         <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3083,25 +2983,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920322</v>
+        <v>20330051920321</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3109,182 +3009,44 @@
         <v>20330051920322</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920397</v>
+        <v>20330051920327</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920397</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920317</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920321</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920329</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920331</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920335</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
